--- a/Vulnerability Test Results/Security_Test_Report_300.xlsx
+++ b/Vulnerability Test Results/Security_Test_Report_300.xlsx
@@ -573,7 +573,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Execution Date: 2026-08-27 10:47:03</t>
+          <t>Execution Date: 2026-08-27 11:55:40</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>~6.12 seconds</t>
+          <t>~6.21 seconds</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
@@ -1173,7 +1173,7 @@
         </is>
       </c>
       <c r="K2" s="7" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         </is>
       </c>
       <c r="K3" s="10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L3" s="10" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="K4" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         </is>
       </c>
       <c r="K5" s="10" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L5" s="10" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="K7" s="10" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="L7" s="10" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="K8" s="7" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="K9" s="10" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="L9" s="10" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         </is>
       </c>
       <c r="K10" s="7" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         </is>
       </c>
       <c r="K11" s="10" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="L11" s="10" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="K12" s="7" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="K13" s="10" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="L13" s="10" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="K14" s="7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         </is>
       </c>
       <c r="K15" s="10" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="L15" s="10" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         </is>
       </c>
       <c r="K16" s="7" t="n">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="K17" s="10" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="L17" s="10" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         </is>
       </c>
       <c r="K18" s="7" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="K19" s="10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L19" s="10" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         </is>
       </c>
       <c r="K20" s="7" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         </is>
       </c>
       <c r="K21" s="10" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="L21" s="10" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="K22" s="7" t="n">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="K23" s="10" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="L23" s="10" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         </is>
       </c>
       <c r="K24" s="7" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="L24" s="7" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         </is>
       </c>
       <c r="K25" s="10" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="L25" s="10" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="K26" s="7" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="K27" s="10" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="L27" s="10" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         </is>
       </c>
       <c r="K28" s="7" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="K29" s="10" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="L29" s="10" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         </is>
       </c>
       <c r="K30" s="7" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="K31" s="10" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L31" s="10" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         </is>
       </c>
       <c r="K32" s="7" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         </is>
       </c>
       <c r="K33" s="10" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="L33" s="10" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         </is>
       </c>
       <c r="K34" s="7" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         </is>
       </c>
       <c r="K35" s="10" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="L35" s="10" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="K36" s="7" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="L36" s="7" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         </is>
       </c>
       <c r="K37" s="10" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L37" s="10" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         </is>
       </c>
       <c r="K38" s="7" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="L38" s="7" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         </is>
       </c>
       <c r="K40" s="7" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         </is>
       </c>
       <c r="K41" s="10" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="L41" s="10" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         </is>
       </c>
       <c r="K42" s="7" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="L42" s="7" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         </is>
       </c>
       <c r="K43" s="10" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="L43" s="10" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         </is>
       </c>
       <c r="K44" s="7" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         </is>
       </c>
       <c r="K45" s="10" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="L45" s="10" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         </is>
       </c>
       <c r="K46" s="7" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="K47" s="10" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="L47" s="10" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="K48" s="7" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         </is>
       </c>
       <c r="K49" s="10" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="L49" s="10" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         </is>
       </c>
       <c r="K50" s="7" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
         </is>
       </c>
       <c r="K51" s="10" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L51" s="10" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         </is>
       </c>
       <c r="K52" s="7" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="K53" s="10" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L53" s="10" t="inlineStr">
         <is>
@@ -4397,7 +4397,7 @@
         </is>
       </c>
       <c r="K54" s="7" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="L54" s="7" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         </is>
       </c>
       <c r="K55" s="10" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="L55" s="10" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         </is>
       </c>
       <c r="K56" s="7" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
@@ -4583,7 +4583,7 @@
         </is>
       </c>
       <c r="K57" s="10" t="n">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="L57" s="10" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         </is>
       </c>
       <c r="K58" s="7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         </is>
       </c>
       <c r="K59" s="10" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="L59" s="10" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="K60" s="7" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         </is>
       </c>
       <c r="K61" s="10" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="L61" s="10" t="inlineStr">
         <is>
@@ -4893,7 +4893,7 @@
         </is>
       </c>
       <c r="K62" s="7" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
         </is>
       </c>
       <c r="K63" s="10" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="L63" s="10" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         </is>
       </c>
       <c r="K64" s="7" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         </is>
       </c>
       <c r="K65" s="10" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L65" s="10" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         </is>
       </c>
       <c r="K66" s="7" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         </is>
       </c>
       <c r="K67" s="10" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="L67" s="10" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         </is>
       </c>
       <c r="K68" s="7" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="K69" s="10" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L69" s="10" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="K70" s="7" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="K72" s="7" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         </is>
       </c>
       <c r="K73" s="10" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="L73" s="10" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
         </is>
       </c>
       <c r="K74" s="7" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         </is>
       </c>
       <c r="K75" s="10" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="L75" s="10" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         </is>
       </c>
       <c r="K76" s="7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L76" s="7" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="K77" s="10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="L77" s="10" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="K78" s="7" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
         </is>
       </c>
       <c r="K79" s="10" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L79" s="10" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
         </is>
       </c>
       <c r="K80" s="7" t="n">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="L80" s="7" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         </is>
       </c>
       <c r="K81" s="10" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="L81" s="10" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
         </is>
       </c>
       <c r="K82" s="7" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="L82" s="7" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         </is>
       </c>
       <c r="K83" s="10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L83" s="10" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         </is>
       </c>
       <c r="K84" s="7" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="L84" s="7" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
         </is>
       </c>
       <c r="K85" s="10" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="L85" s="10" t="inlineStr">
         <is>
@@ -6381,7 +6381,7 @@
         </is>
       </c>
       <c r="K86" s="7" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L86" s="7" t="inlineStr">
         <is>
@@ -6443,7 +6443,7 @@
         </is>
       </c>
       <c r="K87" s="10" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="L87" s="10" t="inlineStr">
         <is>
@@ -6505,7 +6505,7 @@
         </is>
       </c>
       <c r="K88" s="7" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="L88" s="7" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="K89" s="10" t="n">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="L89" s="10" t="inlineStr">
         <is>
@@ -6629,7 +6629,7 @@
         </is>
       </c>
       <c r="K90" s="7" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L90" s="7" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         </is>
       </c>
       <c r="K91" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L91" s="10" t="inlineStr">
         <is>
@@ -6753,7 +6753,7 @@
         </is>
       </c>
       <c r="K92" s="7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L92" s="7" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         </is>
       </c>
       <c r="K93" s="10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L93" s="10" t="inlineStr">
         <is>
@@ -6877,7 +6877,7 @@
         </is>
       </c>
       <c r="K94" s="7" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="L94" s="7" t="inlineStr">
         <is>
@@ -6939,7 +6939,7 @@
         </is>
       </c>
       <c r="K95" s="10" t="n">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="L95" s="10" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         </is>
       </c>
       <c r="K96" s="7" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="L96" s="7" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         </is>
       </c>
       <c r="K97" s="10" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="L97" s="10" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         </is>
       </c>
       <c r="K98" s="7" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="L98" s="7" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="K99" s="10" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="L99" s="10" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         </is>
       </c>
       <c r="K100" s="7" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="L100" s="7" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="K101" s="10" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="L101" s="10" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         </is>
       </c>
       <c r="K102" s="7" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="L102" s="7" t="inlineStr">
         <is>
@@ -7435,7 +7435,7 @@
         </is>
       </c>
       <c r="K103" s="10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L103" s="10" t="inlineStr">
         <is>
@@ -7497,7 +7497,7 @@
         </is>
       </c>
       <c r="K104" s="7" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="L104" s="7" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         </is>
       </c>
       <c r="K105" s="10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L105" s="10" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         </is>
       </c>
       <c r="K106" s="7" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="L106" s="7" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         </is>
       </c>
       <c r="K107" s="10" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="L107" s="10" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         </is>
       </c>
       <c r="K108" s="7" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="L108" s="7" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         </is>
       </c>
       <c r="K109" s="10" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="L109" s="10" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
         </is>
       </c>
       <c r="K110" s="7" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="L110" s="7" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="K111" s="10" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L111" s="10" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         </is>
       </c>
       <c r="K112" s="7" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="L112" s="7" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="K113" s="10" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="L113" s="10" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         </is>
       </c>
       <c r="K114" s="7" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="L114" s="7" t="inlineStr">
         <is>
@@ -8179,7 +8179,7 @@
         </is>
       </c>
       <c r="K115" s="10" t="n">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="L115" s="10" t="inlineStr">
         <is>
@@ -8241,7 +8241,7 @@
         </is>
       </c>
       <c r="K116" s="7" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="L116" s="7" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
         </is>
       </c>
       <c r="K117" s="10" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="L117" s="10" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="K118" s="7" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="L118" s="7" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
         </is>
       </c>
       <c r="K119" s="10" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L119" s="10" t="inlineStr">
         <is>
@@ -8489,7 +8489,7 @@
         </is>
       </c>
       <c r="K120" s="7" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="L120" s="7" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         </is>
       </c>
       <c r="K121" s="10" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="L121" s="10" t="inlineStr">
         <is>
@@ -8613,7 +8613,7 @@
         </is>
       </c>
       <c r="K122" s="7" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="L122" s="7" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         </is>
       </c>
       <c r="K123" s="10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L123" s="10" t="inlineStr">
         <is>
@@ -8737,7 +8737,7 @@
         </is>
       </c>
       <c r="K124" s="7" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="L124" s="7" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         </is>
       </c>
       <c r="K125" s="10" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="L125" s="10" t="inlineStr">
         <is>
@@ -8861,7 +8861,7 @@
         </is>
       </c>
       <c r="K126" s="7" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="L126" s="7" t="inlineStr">
         <is>
@@ -8923,7 +8923,7 @@
         </is>
       </c>
       <c r="K127" s="10" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="L127" s="10" t="inlineStr">
         <is>
@@ -8985,7 +8985,7 @@
         </is>
       </c>
       <c r="K128" s="7" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="L128" s="7" t="inlineStr">
         <is>
@@ -9047,7 +9047,7 @@
         </is>
       </c>
       <c r="K129" s="10" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="L129" s="10" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="K130" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L130" s="7" t="inlineStr">
         <is>
@@ -9171,7 +9171,7 @@
         </is>
       </c>
       <c r="K131" s="10" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="L131" s="10" t="inlineStr">
         <is>
@@ -9233,7 +9233,7 @@
         </is>
       </c>
       <c r="K132" s="7" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L132" s="7" t="inlineStr">
         <is>
@@ -9295,7 +9295,7 @@
         </is>
       </c>
       <c r="K133" s="10" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L133" s="10" t="inlineStr">
         <is>
@@ -9357,7 +9357,7 @@
         </is>
       </c>
       <c r="K134" s="7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="L134" s="7" t="inlineStr">
         <is>
@@ -9419,7 +9419,7 @@
         </is>
       </c>
       <c r="K135" s="10" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="L135" s="10" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         </is>
       </c>
       <c r="K136" s="7" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="L136" s="7" t="inlineStr">
         <is>
@@ -9543,7 +9543,7 @@
         </is>
       </c>
       <c r="K137" s="10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L137" s="10" t="inlineStr">
         <is>
@@ -9605,7 +9605,7 @@
         </is>
       </c>
       <c r="K138" s="7" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="L138" s="7" t="inlineStr">
         <is>
@@ -9667,7 +9667,7 @@
         </is>
       </c>
       <c r="K139" s="10" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="L139" s="10" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
         </is>
       </c>
       <c r="K140" s="7" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="L140" s="7" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         </is>
       </c>
       <c r="K141" s="10" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="L141" s="10" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
         </is>
       </c>
       <c r="K142" s="7" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="L142" s="7" t="inlineStr">
         <is>
@@ -9915,7 +9915,7 @@
         </is>
       </c>
       <c r="K143" s="10" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="L143" s="10" t="inlineStr">
         <is>
@@ -9977,7 +9977,7 @@
         </is>
       </c>
       <c r="K144" s="7" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="L144" s="7" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
         </is>
       </c>
       <c r="K145" s="10" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="L145" s="10" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         </is>
       </c>
       <c r="K146" s="7" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="L146" s="7" t="inlineStr">
         <is>
@@ -10163,7 +10163,7 @@
         </is>
       </c>
       <c r="K147" s="10" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="L147" s="10" t="inlineStr">
         <is>
@@ -10228,7 +10228,7 @@
         </is>
       </c>
       <c r="K148" s="7" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="L148" s="7" t="inlineStr">
         <is>
@@ -10290,7 +10290,7 @@
         </is>
       </c>
       <c r="K149" s="10" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L149" s="10" t="inlineStr">
         <is>
@@ -10352,7 +10352,7 @@
         </is>
       </c>
       <c r="K150" s="7" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="L150" s="7" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         </is>
       </c>
       <c r="K151" s="10" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="L151" s="10" t="inlineStr">
         <is>
@@ -10476,7 +10476,7 @@
         </is>
       </c>
       <c r="K152" s="7" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="L152" s="7" t="inlineStr">
         <is>
@@ -10538,7 +10538,7 @@
         </is>
       </c>
       <c r="K153" s="10" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="L153" s="10" t="inlineStr">
         <is>
@@ -10600,7 +10600,7 @@
         </is>
       </c>
       <c r="K154" s="7" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="L154" s="7" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         </is>
       </c>
       <c r="K155" s="10" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L155" s="10" t="inlineStr">
         <is>
@@ -10724,7 +10724,7 @@
         </is>
       </c>
       <c r="K156" s="7" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L156" s="7" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
         </is>
       </c>
       <c r="K157" s="10" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="L157" s="10" t="inlineStr">
         <is>
@@ -10848,7 +10848,7 @@
         </is>
       </c>
       <c r="K158" s="7" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="L158" s="7" t="inlineStr">
         <is>
@@ -10910,7 +10910,7 @@
         </is>
       </c>
       <c r="K159" s="10" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="L159" s="10" t="inlineStr">
         <is>
@@ -10972,7 +10972,7 @@
         </is>
       </c>
       <c r="K160" s="7" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="L160" s="7" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
         </is>
       </c>
       <c r="K161" s="10" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="L161" s="10" t="inlineStr">
         <is>
@@ -11096,7 +11096,7 @@
         </is>
       </c>
       <c r="K162" s="7" t="n">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="L162" s="7" t="inlineStr">
         <is>
@@ -11158,7 +11158,7 @@
         </is>
       </c>
       <c r="K163" s="10" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="L163" s="10" t="inlineStr">
         <is>
@@ -11220,7 +11220,7 @@
         </is>
       </c>
       <c r="K164" s="7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="L164" s="7" t="inlineStr">
         <is>
@@ -11282,7 +11282,7 @@
         </is>
       </c>
       <c r="K165" s="10" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="L165" s="10" t="inlineStr">
         <is>
@@ -11344,7 +11344,7 @@
         </is>
       </c>
       <c r="K166" s="7" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="L166" s="7" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
         </is>
       </c>
       <c r="K167" s="10" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="L167" s="10" t="inlineStr">
         <is>
@@ -11468,7 +11468,7 @@
         </is>
       </c>
       <c r="K168" s="7" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="L168" s="7" t="inlineStr">
         <is>
@@ -11530,7 +11530,7 @@
         </is>
       </c>
       <c r="K169" s="10" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="L169" s="10" t="inlineStr">
         <is>
@@ -11592,7 +11592,7 @@
         </is>
       </c>
       <c r="K170" s="7" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="L170" s="7" t="inlineStr">
         <is>
@@ -11654,7 +11654,7 @@
         </is>
       </c>
       <c r="K171" s="10" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="L171" s="10" t="inlineStr">
         <is>
@@ -11716,7 +11716,7 @@
         </is>
       </c>
       <c r="K172" s="7" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="L172" s="7" t="inlineStr">
         <is>
@@ -11778,7 +11778,7 @@
         </is>
       </c>
       <c r="K173" s="10" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="L173" s="10" t="inlineStr">
         <is>
@@ -11840,7 +11840,7 @@
         </is>
       </c>
       <c r="K174" s="7" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="L174" s="7" t="inlineStr">
         <is>
@@ -11902,7 +11902,7 @@
         </is>
       </c>
       <c r="K175" s="10" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="L175" s="10" t="inlineStr">
         <is>
@@ -11964,7 +11964,7 @@
         </is>
       </c>
       <c r="K176" s="7" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="L176" s="7" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         </is>
       </c>
       <c r="K177" s="10" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L177" s="10" t="inlineStr">
         <is>
@@ -12088,7 +12088,7 @@
         </is>
       </c>
       <c r="K178" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L178" s="7" t="inlineStr">
         <is>
@@ -12150,7 +12150,7 @@
         </is>
       </c>
       <c r="K179" s="10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L179" s="10" t="inlineStr">
         <is>
@@ -12212,7 +12212,7 @@
         </is>
       </c>
       <c r="K180" s="7" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="L180" s="7" t="inlineStr">
         <is>
@@ -12274,7 +12274,7 @@
         </is>
       </c>
       <c r="K181" s="10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L181" s="10" t="inlineStr">
         <is>
@@ -12336,7 +12336,7 @@
         </is>
       </c>
       <c r="K182" s="7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L182" s="7" t="inlineStr">
         <is>
@@ -12398,7 +12398,7 @@
         </is>
       </c>
       <c r="K183" s="10" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="L183" s="10" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         </is>
       </c>
       <c r="K184" s="7" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="L184" s="7" t="inlineStr">
         <is>
@@ -12522,7 +12522,7 @@
         </is>
       </c>
       <c r="K185" s="10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L185" s="10" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         </is>
       </c>
       <c r="K186" s="7" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="L186" s="7" t="inlineStr">
         <is>
@@ -12646,7 +12646,7 @@
         </is>
       </c>
       <c r="K187" s="10" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="L187" s="10" t="inlineStr">
         <is>
@@ -12708,7 +12708,7 @@
         </is>
       </c>
       <c r="K188" s="7" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="L188" s="7" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         </is>
       </c>
       <c r="K189" s="10" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="L189" s="10" t="inlineStr">
         <is>
@@ -12832,7 +12832,7 @@
         </is>
       </c>
       <c r="K190" s="7" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="L190" s="7" t="inlineStr">
         <is>
@@ -12894,7 +12894,7 @@
         </is>
       </c>
       <c r="K191" s="10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L191" s="10" t="inlineStr">
         <is>
@@ -12956,7 +12956,7 @@
         </is>
       </c>
       <c r="K192" s="7" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="L192" s="7" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         </is>
       </c>
       <c r="K193" s="10" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="L193" s="10" t="inlineStr">
         <is>
@@ -13080,7 +13080,7 @@
         </is>
       </c>
       <c r="K194" s="7" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="L194" s="7" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         </is>
       </c>
       <c r="K195" s="10" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="L195" s="10" t="inlineStr">
         <is>
@@ -13204,7 +13204,7 @@
         </is>
       </c>
       <c r="K196" s="7" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="L196" s="7" t="inlineStr">
         <is>
@@ -13266,7 +13266,7 @@
         </is>
       </c>
       <c r="K197" s="10" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="L197" s="10" t="inlineStr">
         <is>
@@ -13328,7 +13328,7 @@
         </is>
       </c>
       <c r="K198" s="7" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="L198" s="7" t="inlineStr">
         <is>
@@ -13390,7 +13390,7 @@
         </is>
       </c>
       <c r="K199" s="10" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="L199" s="10" t="inlineStr">
         <is>
@@ -13452,7 +13452,7 @@
         </is>
       </c>
       <c r="K200" s="7" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L200" s="7" t="inlineStr">
         <is>
@@ -13514,7 +13514,7 @@
         </is>
       </c>
       <c r="K201" s="10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="L201" s="10" t="inlineStr">
         <is>
@@ -13576,7 +13576,7 @@
         </is>
       </c>
       <c r="K202" s="7" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="L202" s="7" t="inlineStr">
         <is>
@@ -13638,7 +13638,7 @@
         </is>
       </c>
       <c r="K203" s="10" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="L203" s="10" t="inlineStr">
         <is>
@@ -13700,7 +13700,7 @@
         </is>
       </c>
       <c r="K204" s="7" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="L204" s="7" t="inlineStr">
         <is>
@@ -13762,7 +13762,7 @@
         </is>
       </c>
       <c r="K205" s="10" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L205" s="10" t="inlineStr">
         <is>
@@ -13824,7 +13824,7 @@
         </is>
       </c>
       <c r="K206" s="7" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L206" s="7" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
         </is>
       </c>
       <c r="K207" s="10" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="L207" s="10" t="inlineStr">
         <is>
@@ -13948,7 +13948,7 @@
         </is>
       </c>
       <c r="K208" s="7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L208" s="7" t="inlineStr">
         <is>
@@ -14010,7 +14010,7 @@
         </is>
       </c>
       <c r="K209" s="10" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="L209" s="10" t="inlineStr">
         <is>
@@ -14072,7 +14072,7 @@
         </is>
       </c>
       <c r="K210" s="7" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L210" s="7" t="inlineStr">
         <is>
@@ -14134,7 +14134,7 @@
         </is>
       </c>
       <c r="K211" s="10" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L211" s="10" t="inlineStr">
         <is>
@@ -14196,7 +14196,7 @@
         </is>
       </c>
       <c r="K212" s="7" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="L212" s="7" t="inlineStr">
         <is>
@@ -14258,7 +14258,7 @@
         </is>
       </c>
       <c r="K213" s="10" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="L213" s="10" t="inlineStr">
         <is>
@@ -14382,7 +14382,7 @@
         </is>
       </c>
       <c r="K215" s="10" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="L215" s="10" t="inlineStr">
         <is>
@@ -14444,7 +14444,7 @@
         </is>
       </c>
       <c r="K216" s="7" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="L216" s="7" t="inlineStr">
         <is>
@@ -14506,7 +14506,7 @@
         </is>
       </c>
       <c r="K217" s="10" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="L217" s="10" t="inlineStr">
         <is>
@@ -14568,7 +14568,7 @@
         </is>
       </c>
       <c r="K218" s="7" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="L218" s="7" t="inlineStr">
         <is>
@@ -14692,7 +14692,7 @@
         </is>
       </c>
       <c r="K220" s="7" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="L220" s="7" t="inlineStr">
         <is>
@@ -14754,7 +14754,7 @@
         </is>
       </c>
       <c r="K221" s="10" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="L221" s="10" t="inlineStr">
         <is>
@@ -14816,7 +14816,7 @@
         </is>
       </c>
       <c r="K222" s="7" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="L222" s="7" t="inlineStr">
         <is>
@@ -14878,7 +14878,7 @@
         </is>
       </c>
       <c r="K223" s="10" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="L223" s="10" t="inlineStr">
         <is>
@@ -14940,7 +14940,7 @@
         </is>
       </c>
       <c r="K224" s="7" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="L224" s="7" t="inlineStr">
         <is>
@@ -15002,7 +15002,7 @@
         </is>
       </c>
       <c r="K225" s="10" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="L225" s="10" t="inlineStr">
         <is>
@@ -15064,7 +15064,7 @@
         </is>
       </c>
       <c r="K226" s="7" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="L226" s="7" t="inlineStr">
         <is>
@@ -15126,7 +15126,7 @@
         </is>
       </c>
       <c r="K227" s="10" t="n">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="L227" s="10" t="inlineStr">
         <is>
@@ -15188,7 +15188,7 @@
         </is>
       </c>
       <c r="K228" s="7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L228" s="7" t="inlineStr">
         <is>
@@ -15250,7 +15250,7 @@
         </is>
       </c>
       <c r="K229" s="10" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="L229" s="10" t="inlineStr">
         <is>
@@ -15312,7 +15312,7 @@
         </is>
       </c>
       <c r="K230" s="7" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="L230" s="7" t="inlineStr">
         <is>
@@ -15374,7 +15374,7 @@
         </is>
       </c>
       <c r="K231" s="10" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="L231" s="10" t="inlineStr">
         <is>
@@ -15436,7 +15436,7 @@
         </is>
       </c>
       <c r="K232" s="7" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="L232" s="7" t="inlineStr">
         <is>
@@ -15498,7 +15498,7 @@
         </is>
       </c>
       <c r="K233" s="10" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="L233" s="10" t="inlineStr">
         <is>
@@ -15560,7 +15560,7 @@
         </is>
       </c>
       <c r="K234" s="7" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L234" s="7" t="inlineStr">
         <is>
@@ -15622,7 +15622,7 @@
         </is>
       </c>
       <c r="K235" s="10" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="L235" s="10" t="inlineStr">
         <is>
@@ -15684,7 +15684,7 @@
         </is>
       </c>
       <c r="K236" s="7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L236" s="7" t="inlineStr">
         <is>
@@ -15746,7 +15746,7 @@
         </is>
       </c>
       <c r="K237" s="10" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="L237" s="10" t="inlineStr">
         <is>
@@ -15808,7 +15808,7 @@
         </is>
       </c>
       <c r="K238" s="7" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="L238" s="7" t="inlineStr">
         <is>
@@ -15870,7 +15870,7 @@
         </is>
       </c>
       <c r="K239" s="10" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="L239" s="10" t="inlineStr">
         <is>
@@ -15932,7 +15932,7 @@
         </is>
       </c>
       <c r="K240" s="7" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L240" s="7" t="inlineStr">
         <is>
@@ -15994,7 +15994,7 @@
         </is>
       </c>
       <c r="K241" s="10" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L241" s="10" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         </is>
       </c>
       <c r="K242" s="7" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="L242" s="7" t="inlineStr">
         <is>
@@ -16118,7 +16118,7 @@
         </is>
       </c>
       <c r="K243" s="10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L243" s="10" t="inlineStr">
         <is>
@@ -16180,7 +16180,7 @@
         </is>
       </c>
       <c r="K244" s="7" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L244" s="7" t="inlineStr">
         <is>
@@ -16242,7 +16242,7 @@
         </is>
       </c>
       <c r="K245" s="10" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="L245" s="10" t="inlineStr">
         <is>
@@ -16304,7 +16304,7 @@
         </is>
       </c>
       <c r="K246" s="7" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="L246" s="7" t="inlineStr">
         <is>
@@ -16366,7 +16366,7 @@
         </is>
       </c>
       <c r="K247" s="10" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="L247" s="10" t="inlineStr">
         <is>
@@ -16428,7 +16428,7 @@
         </is>
       </c>
       <c r="K248" s="7" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="L248" s="7" t="inlineStr">
         <is>
@@ -16490,7 +16490,7 @@
         </is>
       </c>
       <c r="K249" s="10" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="L249" s="10" t="inlineStr">
         <is>
@@ -16552,7 +16552,7 @@
         </is>
       </c>
       <c r="K250" s="7" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="L250" s="7" t="inlineStr">
         <is>
@@ -16614,7 +16614,7 @@
         </is>
       </c>
       <c r="K251" s="10" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="L251" s="10" t="inlineStr">
         <is>
@@ -16676,7 +16676,7 @@
         </is>
       </c>
       <c r="K252" s="7" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="L252" s="7" t="inlineStr">
         <is>
@@ -16738,7 +16738,7 @@
         </is>
       </c>
       <c r="K253" s="10" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="L253" s="10" t="inlineStr">
         <is>
@@ -16800,7 +16800,7 @@
         </is>
       </c>
       <c r="K254" s="7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L254" s="7" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         </is>
       </c>
       <c r="K255" s="10" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="L255" s="10" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         </is>
       </c>
       <c r="K256" s="7" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="L256" s="7" t="inlineStr">
         <is>
@@ -16986,7 +16986,7 @@
         </is>
       </c>
       <c r="K257" s="10" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L257" s="10" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         </is>
       </c>
       <c r="K258" s="7" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="L258" s="7" t="inlineStr">
         <is>
@@ -17110,7 +17110,7 @@
         </is>
       </c>
       <c r="K259" s="10" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="L259" s="10" t="inlineStr">
         <is>
@@ -17172,7 +17172,7 @@
         </is>
       </c>
       <c r="K260" s="7" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="L260" s="7" t="inlineStr">
         <is>
@@ -17234,7 +17234,7 @@
         </is>
       </c>
       <c r="K261" s="10" t="n">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="L261" s="10" t="inlineStr">
         <is>
@@ -17296,7 +17296,7 @@
         </is>
       </c>
       <c r="K262" s="7" t="n">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="L262" s="7" t="inlineStr">
         <is>
@@ -17358,7 +17358,7 @@
         </is>
       </c>
       <c r="K263" s="10" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="L263" s="10" t="inlineStr">
         <is>
@@ -17420,7 +17420,7 @@
         </is>
       </c>
       <c r="K264" s="7" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="L264" s="7" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         </is>
       </c>
       <c r="K265" s="10" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="L265" s="10" t="inlineStr">
         <is>
@@ -17544,7 +17544,7 @@
         </is>
       </c>
       <c r="K266" s="7" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="L266" s="7" t="inlineStr">
         <is>
@@ -17606,7 +17606,7 @@
         </is>
       </c>
       <c r="K267" s="10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L267" s="10" t="inlineStr">
         <is>
@@ -17668,7 +17668,7 @@
         </is>
       </c>
       <c r="K268" s="7" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="L268" s="7" t="inlineStr">
         <is>
@@ -17730,7 +17730,7 @@
         </is>
       </c>
       <c r="K269" s="10" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="L269" s="10" t="inlineStr">
         <is>
@@ -17792,7 +17792,7 @@
         </is>
       </c>
       <c r="K270" s="7" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="L270" s="7" t="inlineStr">
         <is>
@@ -17854,7 +17854,7 @@
         </is>
       </c>
       <c r="K271" s="10" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="L271" s="10" t="inlineStr">
         <is>
@@ -17916,7 +17916,7 @@
         </is>
       </c>
       <c r="K272" s="7" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L272" s="7" t="inlineStr">
         <is>
@@ -17978,7 +17978,7 @@
         </is>
       </c>
       <c r="K273" s="10" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="L273" s="10" t="inlineStr">
         <is>
@@ -18040,7 +18040,7 @@
         </is>
       </c>
       <c r="K274" s="7" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="L274" s="7" t="inlineStr">
         <is>
@@ -18102,7 +18102,7 @@
         </is>
       </c>
       <c r="K275" s="10" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="L275" s="10" t="inlineStr">
         <is>
@@ -18164,7 +18164,7 @@
         </is>
       </c>
       <c r="K276" s="7" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="L276" s="7" t="inlineStr">
         <is>
@@ -18226,7 +18226,7 @@
         </is>
       </c>
       <c r="K277" s="10" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="L277" s="10" t="inlineStr">
         <is>
@@ -18288,7 +18288,7 @@
         </is>
       </c>
       <c r="K278" s="7" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="L278" s="7" t="inlineStr">
         <is>
@@ -18350,7 +18350,7 @@
         </is>
       </c>
       <c r="K279" s="10" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L279" s="10" t="inlineStr">
         <is>
@@ -18412,7 +18412,7 @@
         </is>
       </c>
       <c r="K280" s="7" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="L280" s="7" t="inlineStr">
         <is>
@@ -18474,7 +18474,7 @@
         </is>
       </c>
       <c r="K281" s="10" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="L281" s="10" t="inlineStr">
         <is>
@@ -18536,7 +18536,7 @@
         </is>
       </c>
       <c r="K282" s="7" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="L282" s="7" t="inlineStr">
         <is>
@@ -18598,7 +18598,7 @@
         </is>
       </c>
       <c r="K283" s="10" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="L283" s="10" t="inlineStr">
         <is>
@@ -18660,7 +18660,7 @@
         </is>
       </c>
       <c r="K284" s="7" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="L284" s="7" t="inlineStr">
         <is>
@@ -18722,7 +18722,7 @@
         </is>
       </c>
       <c r="K285" s="10" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="L285" s="10" t="inlineStr">
         <is>
@@ -18784,7 +18784,7 @@
         </is>
       </c>
       <c r="K286" s="7" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L286" s="7" t="inlineStr">
         <is>
@@ -18846,7 +18846,7 @@
         </is>
       </c>
       <c r="K287" s="10" t="n">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="L287" s="10" t="inlineStr">
         <is>
@@ -18908,7 +18908,7 @@
         </is>
       </c>
       <c r="K288" s="7" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="L288" s="7" t="inlineStr">
         <is>
@@ -18970,7 +18970,7 @@
         </is>
       </c>
       <c r="K289" s="10" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="L289" s="10" t="inlineStr">
         <is>
@@ -19032,7 +19032,7 @@
         </is>
       </c>
       <c r="K290" s="7" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="L290" s="7" t="inlineStr">
         <is>
@@ -19094,7 +19094,7 @@
         </is>
       </c>
       <c r="K291" s="10" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="L291" s="10" t="inlineStr">
         <is>
@@ -19156,7 +19156,7 @@
         </is>
       </c>
       <c r="K292" s="7" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="L292" s="7" t="inlineStr">
         <is>
@@ -19218,7 +19218,7 @@
         </is>
       </c>
       <c r="K293" s="10" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="L293" s="10" t="inlineStr">
         <is>
@@ -19280,7 +19280,7 @@
         </is>
       </c>
       <c r="K294" s="7" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="L294" s="7" t="inlineStr">
         <is>
@@ -19342,7 +19342,7 @@
         </is>
       </c>
       <c r="K295" s="10" t="n">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="L295" s="10" t="inlineStr">
         <is>
@@ -19404,7 +19404,7 @@
         </is>
       </c>
       <c r="K296" s="7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L296" s="7" t="inlineStr">
         <is>
